--- a/public/exports/32264328.xlsx
+++ b/public/exports/32264328.xlsx
@@ -81,7 +81,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4191418</t>
+          <t xml:space="preserve">369803</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -90,7 +90,7 @@
         </is>
       </c>
       <c r="F2">
-        <v>417</v>
+        <v>545</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -131,16 +131,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4194186</t>
+          <t xml:space="preserve">4191418</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F3">
-        <v>266</v>
+        <v>417</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -181,16 +181,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4194793</t>
+          <t xml:space="preserve">4194186</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F4">
-        <v>1607</v>
+        <v>266</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -231,16 +231,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">4194793</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F5">
-        <v>629</v>
+        <v>1607</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -281,16 +281,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197392</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F6">
-        <v>257</v>
+        <v>629</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -331,16 +331,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">4199045</t>
+          <t xml:space="preserve">4197392</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F7">
-        <v>500</v>
+        <v>257</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -381,16 +381,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4199447</t>
+          <t xml:space="preserve">4199045</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F8">
-        <v>759</v>
+        <v>500</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -781,25 +781,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">9995805</t>
+          <t xml:space="preserve">4199447</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F16">
-        <v>329</v>
+        <v>759</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">311088099</t>
+          <t xml:space="preserve">200026991</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-12-15</t>
+          <t xml:space="preserve">2020-01-19</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1736,15 +1736,15 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F35">
-        <v>428</v>
+        <v>329</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221240</t>
+          <t xml:space="preserve">311221242</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1786,11 +1786,11 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F36">
-        <v>1621</v>
+        <v>428</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1831,25 +1831,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">100049247</t>
+          <t xml:space="preserve">9995805</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F37">
-        <v>620</v>
+        <v>1621</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224995</t>
+          <t xml:space="preserve">311221240</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-27</t>
+          <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">4193434</t>
+          <t xml:space="preserve">100049247</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1890,16 +1890,16 @@
         </is>
       </c>
       <c r="F38">
-        <v>2202</v>
+        <v>620</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230442</t>
+          <t xml:space="preserve">311224995</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-24</t>
+          <t xml:space="preserve">2027-01-27</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">7349419</t>
+          <t xml:space="preserve">4193434</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1940,11 +1940,11 @@
         </is>
       </c>
       <c r="F39">
-        <v>11918</v>
+        <v>2202</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230441</t>
+          <t xml:space="preserve">311230442</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">8375804</t>
+          <t xml:space="preserve">7349419</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1990,16 +1990,16 @@
         </is>
       </c>
       <c r="F40">
-        <v>994</v>
+        <v>11918</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311242492</t>
+          <t xml:space="preserve">311230441</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-24</t>
+          <t xml:space="preserve">2027-02-24</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2036,11 +2036,11 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F41">
-        <v>1212</v>
+        <v>994</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2086,11 +2086,11 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F42">
-        <v>1546</v>
+        <v>1212</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2131,25 +2131,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196620</t>
+          <t xml:space="preserve">8375804</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F43">
-        <v>887</v>
+        <v>1546</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253199</t>
+          <t xml:space="preserve">311242492</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-12</t>
+          <t xml:space="preserve">2027-04-24</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052507</t>
+          <t xml:space="preserve">4196620</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2190,16 +2190,16 @@
         </is>
       </c>
       <c r="F44">
-        <v>787</v>
+        <v>887</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258871</t>
+          <t xml:space="preserve">311253199</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-06-12</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F45">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F46">
@@ -2336,15 +2336,15 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F47">
-        <v>324</v>
+        <v>787</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258869</t>
+          <t xml:space="preserve">311258871</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2386,15 +2386,15 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F48">
-        <v>787</v>
+        <v>324</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258871</t>
+          <t xml:space="preserve">311258869</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F49">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F50">
@@ -2531,25 +2531,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196668</t>
+          <t xml:space="preserve">100052507</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F51">
-        <v>1377</v>
+        <v>787</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259724</t>
+          <t xml:space="preserve">311258871</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196792</t>
+          <t xml:space="preserve">4196668</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2590,11 +2590,11 @@
         </is>
       </c>
       <c r="F52">
-        <v>1063</v>
+        <v>1377</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259573</t>
+          <t xml:space="preserve">311259724</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2636,11 +2636,11 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F53">
-        <v>1468</v>
+        <v>1063</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2681,25 +2681,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196607</t>
+          <t xml:space="preserve">4196792</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F54">
-        <v>3261</v>
+        <v>1468</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311270273</t>
+          <t xml:space="preserve">311259573</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-01</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2736,15 +2736,15 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F55">
-        <v>301</v>
+        <v>3261</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311270275</t>
+          <t xml:space="preserve">311270273</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2786,11 +2786,11 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F56">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2831,25 +2831,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">369803</t>
+          <t xml:space="preserve">4196607</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F57">
-        <v>545</v>
+        <v>310</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311271441</t>
+          <t xml:space="preserve">311270275</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-07</t>
+          <t xml:space="preserve">2027-09-01</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">

--- a/public/exports/32264328.xlsx
+++ b/public/exports/32264328.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:L82"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -29,35 +29,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Adresse</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postnr.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t xml:space="preserve">BFE-nummer</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bygningsnummer</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">Areal (m²)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">EM-nummer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -81,33 +91,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stenslund 2</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t xml:space="preserve">369803</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>545</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -131,33 +151,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Alrøvej 357</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t xml:space="preserve">4191418</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>417</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -181,33 +211,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havnegade 4B</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t xml:space="preserve">4194186</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>266</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -231,33 +271,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Landevejen 30</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8350</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t xml:space="preserve">4194793</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>1607</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -281,33 +331,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vitavej 60</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t xml:space="preserve">4196608</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
         </is>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>629</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -331,33 +391,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Højmarkvej 10</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t xml:space="preserve">4197392</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>257</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -381,33 +451,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Møllevej 3</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t xml:space="preserve">4199045</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>500</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -431,33 +511,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tunø Hovedgade 10</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8799</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t xml:space="preserve">4248229</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>421</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -481,33 +571,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nølevvej 6</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t xml:space="preserve">7349415</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>3084</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -531,33 +631,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stenslund 7</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t xml:space="preserve">8097328</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>312</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -581,33 +691,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stenslund 7</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t xml:space="preserve">8097328</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>251</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -631,33 +751,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vennelundsvej 95</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t xml:space="preserve">8375804</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>994</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -681,33 +811,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vennelundsvej 95</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t xml:space="preserve">8375804</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>2372</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -731,33 +871,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 65</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t xml:space="preserve">8567114, 100197236</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>2273</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -781,33 +931,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Holsteinsgade 43A</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t xml:space="preserve">4199447</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>759</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t xml:space="preserve">200026991</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-01-19</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -831,33 +991,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Solhøjvej 12</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8350</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t xml:space="preserve">4195321</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>371</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve">311203243</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-28</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -881,33 +1051,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Aahavevej 10</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t xml:space="preserve">4197460</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>253</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t xml:space="preserve">311203234</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-28</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -931,33 +1111,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Egholmvej 2</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t xml:space="preserve">4197672</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>512</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve">311203242</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-28</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -981,33 +1171,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Egholmvej 6</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t xml:space="preserve">4197674</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>276</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve">311203232</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-28</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1031,33 +1231,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Egholmvej 6</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t xml:space="preserve">4197674</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>282</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve">311203232</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-28</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1081,33 +1291,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Egholmvej 6</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t xml:space="preserve">4197674</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F22">
+      <c r="H22">
         <v>294</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve">311203232</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-28</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1131,33 +1351,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Egholmvej 6</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t xml:space="preserve">4197674</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>499</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve">311203232</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-28</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1181,33 +1411,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bronzealdervej 16</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t xml:space="preserve">4197674</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>270</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve">311208182</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1231,33 +1471,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Saloparken 2</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t xml:space="preserve">7255382</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>555</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t xml:space="preserve">311208186</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1281,33 +1531,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Torvald Køhlsvej 50</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t xml:space="preserve">9665232</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>398</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t xml:space="preserve">311208185</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1331,33 +1591,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gylling Skolegade 12</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t xml:space="preserve">4193329</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F27">
+      <c r="H27">
         <v>442</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t xml:space="preserve">311211745</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-11-11</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1381,33 +1651,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havrevænget 15</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t xml:space="preserve">8037533</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>327</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t xml:space="preserve">311211743</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-11-11</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1431,33 +1711,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolegade 15A</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t xml:space="preserve">4193708</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F29">
+      <c r="H29">
         <v>398</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t xml:space="preserve">311218214</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1481,33 +1771,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Venneslaparken 1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t xml:space="preserve">7956622</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F30">
+      <c r="H30">
         <v>480</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t xml:space="preserve">311218471</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-12-19</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1531,33 +1831,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevænget 1</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t xml:space="preserve">4193843</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>3079</v>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t xml:space="preserve">311221268</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1581,33 +1891,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevænget 1</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t xml:space="preserve">4193843</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F32">
+      <c r="H32">
         <v>695</v>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t xml:space="preserve">311221268</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1631,33 +1951,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Landevejen 30</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8350</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t xml:space="preserve">4194779</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>275</v>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t xml:space="preserve">311221278</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1681,33 +2011,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rudevej 100</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t xml:space="preserve">9995805</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F34">
+      <c r="H34">
         <v>894</v>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t xml:space="preserve">311221240</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1731,33 +2071,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rudevej 100</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t xml:space="preserve">9995805</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
         </is>
       </c>
-      <c r="F35">
+      <c r="H35">
         <v>329</v>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t xml:space="preserve">311221242</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1781,33 +2131,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rudevej 100</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t xml:space="preserve">9995805</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>428</v>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t xml:space="preserve">311221240</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1831,33 +2191,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rudevej 100</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t xml:space="preserve">9995805</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F37">
+      <c r="H37">
         <v>1621</v>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t xml:space="preserve">311221240</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1881,33 +2251,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østermarksvej 25A</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t xml:space="preserve">100049247</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F38">
+      <c r="H38">
         <v>620</v>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t xml:space="preserve">311224995</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-01-27</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1931,33 +2311,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gylling Skolegade 13</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t xml:space="preserve">4193434</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>2202</v>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t xml:space="preserve">311230442</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-02-24</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1981,33 +2371,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nølevvej 4</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t xml:space="preserve">7349419</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>11918</v>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t xml:space="preserve">311230441</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-02-24</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2031,33 +2431,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vennelundsvej 95</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t xml:space="preserve">8375804</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F41">
+      <c r="H41">
         <v>994</v>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t xml:space="preserve">311242492</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-04-24</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2081,33 +2491,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vennelundsvej 95</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t xml:space="preserve">8375804</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>1212</v>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t xml:space="preserve">311242492</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-04-24</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2131,33 +2551,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vennelundsvej 95</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t xml:space="preserve">8375804</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>1546</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t xml:space="preserve">311242492</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-04-24</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2181,33 +2611,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mejerivej 14</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t xml:space="preserve">4196620</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F44">
+      <c r="H44">
         <v>887</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t xml:space="preserve">311253199</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-06-12</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2231,33 +2671,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bronzealdervej 2</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t xml:space="preserve">100052507</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F45">
+      <c r="H45">
         <v>787</v>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t xml:space="preserve">311258871</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2281,33 +2731,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bronzealdervej 4</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t xml:space="preserve">100052507</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F46">
+      <c r="H46">
         <v>787</v>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t xml:space="preserve">311258871</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2331,33 +2791,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bronzealdervej 6</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t xml:space="preserve">100052507</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F47">
+      <c r="H47">
         <v>787</v>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t xml:space="preserve">311258871</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2381,33 +2851,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bronzealdervej 8</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t xml:space="preserve">100052507</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>324</v>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t xml:space="preserve">311258869</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2431,33 +2911,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bronzealdervej 10</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t xml:space="preserve">100052507</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F49">
+      <c r="H49">
         <v>787</v>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t xml:space="preserve">311258871</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2481,33 +2971,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bronzealdervej 12</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t xml:space="preserve">100052507</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F50">
+      <c r="H50">
         <v>787</v>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t xml:space="preserve">311258871</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2531,33 +3031,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bronzealdervej 14</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t xml:space="preserve">100052507</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F51">
+      <c r="H51">
         <v>787</v>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t xml:space="preserve">311258871</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2581,33 +3091,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rådhusgade 38</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t xml:space="preserve">4196668</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F52">
+      <c r="H52">
         <v>1377</v>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t xml:space="preserve">311259724</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2631,33 +3151,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rådhusgade 43</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t xml:space="preserve">4196792</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F53">
+      <c r="H53">
         <v>1063</v>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t xml:space="preserve">311259573</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2681,33 +3211,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rådhusgade 43</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t xml:space="preserve">4196792</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F54">
+      <c r="H54">
         <v>1468</v>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t xml:space="preserve">311259573</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2731,33 +3271,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ålykkecentret 5</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t xml:space="preserve">4196607</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F55">
+      <c r="H55">
         <v>3261</v>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t xml:space="preserve">311270273</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-09-01</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2781,33 +3331,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t xml:space="preserve">Aaholmsgade 3A</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t xml:space="preserve">4196607</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F56">
+      <c r="H56">
         <v>301</v>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t xml:space="preserve">311270275</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-09-01</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2831,33 +3391,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Aaholmsgade 3E</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t xml:space="preserve">4196607</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F57">
+      <c r="H57">
         <v>310</v>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t xml:space="preserve">311270275</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-09-01</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2881,33 +3451,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stenslund 7</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t xml:space="preserve">8097328</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F58">
+      <c r="H58">
         <v>556</v>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t xml:space="preserve">311275612</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-09-28</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2931,33 +3511,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rådhusgade 3</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t xml:space="preserve">4197028</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F59">
+      <c r="H59">
         <v>6516</v>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t xml:space="preserve">311275868</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-09-29</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2981,33 +3571,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rosensgade 10A</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
           <t xml:space="preserve">4197085</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F60">
+      <c r="H60">
         <v>505</v>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t xml:space="preserve">311276014</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-09-29</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3031,33 +3631,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Banegårdsgade 5</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t xml:space="preserve">8297681</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F61">
+      <c r="H61">
         <v>700</v>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t xml:space="preserve">311275892</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-09-29</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3081,33 +3691,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Holsteinsgade 43</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t xml:space="preserve">4199447</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F62">
+      <c r="H62">
         <v>8417</v>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t xml:space="preserve">311287701</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-07</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3131,33 +3751,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stenslund 6</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t xml:space="preserve">8331220</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F63">
+      <c r="H63">
         <v>719</v>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311447305</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311447313</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-07-01</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3181,33 +3811,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vitaparkvej 9</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t xml:space="preserve">4196608</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F64">
+      <c r="H64">
         <v>1592</v>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t xml:space="preserve">311555235</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3231,33 +3871,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vitaparkvej 9</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t xml:space="preserve">4196608</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="F65">
+      <c r="H65">
         <v>3377</v>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t xml:space="preserve">311555232</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3281,33 +3931,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vitavej 63</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t xml:space="preserve">4196608</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="F66">
+      <c r="H66">
         <v>500</v>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t xml:space="preserve">311555232</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3331,33 +3991,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vitaparkvej 19</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t xml:space="preserve">4196608</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
         </is>
       </c>
-      <c r="F67">
+      <c r="H67">
         <v>1496</v>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t xml:space="preserve">311555236</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3381,33 +4051,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vitavej 71</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t xml:space="preserve">4196608</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c r="F68">
+      <c r="H68">
         <v>2608</v>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t xml:space="preserve">311555232</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3431,33 +4111,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vitaparkvej 17</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t xml:space="preserve">4196608</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t xml:space="preserve">30</t>
         </is>
       </c>
-      <c r="F69">
+      <c r="H69">
         <v>394</v>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t xml:space="preserve">311555232</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3481,33 +4171,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Præstevænget 28</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t xml:space="preserve">4196608</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F70">
+      <c r="H70">
         <v>1313</v>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t xml:space="preserve">311555233</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3531,33 +4231,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vitaparkvej 6</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t xml:space="preserve">4196608</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F71">
+      <c r="H71">
         <v>801</v>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t xml:space="preserve">311555234</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3581,33 +4291,43 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tofts Vænge 1</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t xml:space="preserve">100439978</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F72">
+      <c r="H72">
         <v>1105</v>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t xml:space="preserve">311654677</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-01-18</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3631,33 +4351,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vitaparkvej 1</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t xml:space="preserve">4196608</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F73">
+      <c r="H73">
         <v>5018</v>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t xml:space="preserve">311663627</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-03-02</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3681,33 +4411,43 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevænget 3</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t xml:space="preserve">4193843</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F74">
+      <c r="H74">
         <v>1056</v>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t xml:space="preserve">311872142</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-12-08</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
+      <c r="K74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3731,33 +4471,43 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lundevej 35A</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t xml:space="preserve">10081243</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F75">
+      <c r="H75">
         <v>850</v>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t xml:space="preserve">311915753</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3781,33 +4531,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Højmarkvej 10</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t xml:space="preserve">4197393</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F76">
+      <c r="H76">
         <v>898</v>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t xml:space="preserve">311915775</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3831,33 +4591,43 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østermarksvej 21</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t xml:space="preserve">4198344</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F77">
+      <c r="H77">
         <v>569</v>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t xml:space="preserve">311915750</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
+      <c r="K77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3881,33 +4651,43 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østermarksvej 21B</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t xml:space="preserve">4198348</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F78">
+      <c r="H78">
         <v>555</v>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t xml:space="preserve">311915749</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
+      <c r="K78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3931,33 +4711,43 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t xml:space="preserve">Parkvej 5</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t xml:space="preserve">500006, 4198718</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F79">
+      <c r="H79">
         <v>1568</v>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t xml:space="preserve">311915754</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3981,33 +4771,43 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Parkvej 5</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t xml:space="preserve">500006, 4198718</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F80">
+      <c r="H80">
         <v>1560</v>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t xml:space="preserve">311915754</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4031,33 +4831,43 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Parkvej 5</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t xml:space="preserve">500006, 500007, 4198718</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="F81">
+      <c r="H81">
         <v>3017</v>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t xml:space="preserve">311915754</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
+      <c r="K81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4081,39 +4891,49 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Parkvej 5</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8300</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t xml:space="preserve">500007, 4198718</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F82">
+      <c r="H82">
         <v>332</v>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t xml:space="preserve">311915756</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
+      <c r="K82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J82"/>
+  <autoFilter ref="A1:L82"/>
 </worksheet>
 </file>
--- a/public/exports/32264328.xlsx
+++ b/public/exports/32264328.xlsx
@@ -91,7 +91,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenslund 2</t>
+          <t xml:space="preserve">Alrøvej 357</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -101,7 +101,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">369803</t>
+          <t xml:space="preserve">4191418</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -110,7 +110,7 @@
         </is>
       </c>
       <c r="H2">
-        <v>545</v>
+        <v>417</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,7 +151,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alrøvej 357</t>
+          <t xml:space="preserve">Havnegade 4B</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -161,16 +161,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4191418</t>
+          <t xml:space="preserve">4194186</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H3">
-        <v>417</v>
+        <v>266</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,7 +211,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnegade 4B</t>
+          <t xml:space="preserve">Højmarkvej 10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -221,16 +221,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4194186</t>
+          <t xml:space="preserve">4197392</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H4">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -331,7 +331,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitavej 60</t>
+          <t xml:space="preserve">Møllevej 3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -341,16 +341,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196608</t>
+          <t xml:space="preserve">4199045</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H6">
-        <v>629</v>
+        <v>500</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,7 +391,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarkvej 10</t>
+          <t xml:space="preserve">Nølevvej 6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -401,16 +401,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197392</t>
+          <t xml:space="preserve">7349415</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H7">
-        <v>257</v>
+        <v>3084</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,7 +451,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevej 3</t>
+          <t xml:space="preserve">Skolegade 65</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -461,16 +461,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4199045</t>
+          <t xml:space="preserve">8567114, 100197236</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H8">
-        <v>500</v>
+        <v>2273</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,17 +511,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tunø Hovedgade 10</t>
+          <t xml:space="preserve">Stenslund 7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">8799</t>
+          <t xml:space="preserve">8300</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">4248229</t>
+          <t xml:space="preserve">8097328</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="H9">
-        <v>421</v>
+        <v>312</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nølevvej 6</t>
+          <t xml:space="preserve">Stenslund 7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -581,16 +581,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">7349415</t>
+          <t xml:space="preserve">8097328</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H10">
-        <v>3084</v>
+        <v>251</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,17 +631,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenslund 7</t>
+          <t xml:space="preserve">Tunø Hovedgade 10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">8300</t>
+          <t xml:space="preserve">8799</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097328</t>
+          <t xml:space="preserve">4248229</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="H11">
-        <v>312</v>
+        <v>421</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenslund 7</t>
+          <t xml:space="preserve">Vennelundsvej 95</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -701,16 +701,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">8097328</t>
+          <t xml:space="preserve">8375804</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H12">
-        <v>251</v>
+        <v>994</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -766,11 +766,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H13">
-        <v>994</v>
+        <v>2372</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vennelundsvej 95</t>
+          <t xml:space="preserve">Vitavej 60</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -821,16 +821,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">8375804</t>
+          <t xml:space="preserve">4196608</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H14">
-        <v>2372</v>
+        <v>629</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 65</t>
+          <t xml:space="preserve">Holsteinsgade 43A</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -881,30 +881,30 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">8567114, 100197236</t>
+          <t xml:space="preserve">4199447</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H15">
-        <v>2273</v>
+        <v>759</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200026991</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-01-19</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holsteinsgade 43A</t>
+          <t xml:space="preserve">Aahavevej 10</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -941,35 +941,35 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">4199447</t>
+          <t xml:space="preserve">4197460</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H16">
-        <v>759</v>
+        <v>253</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026991</t>
+          <t xml:space="preserve">311203234</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-19</t>
+          <t xml:space="preserve">2026-09-28</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -991,30 +991,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solhøjvej 12</t>
+          <t xml:space="preserve">Egholmvej 2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">8350</t>
+          <t xml:space="preserve">8300</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">4195321</t>
+          <t xml:space="preserve">4197672</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H17">
-        <v>371</v>
+        <v>512</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203243</t>
+          <t xml:space="preserve">311203242</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aahavevej 10</t>
+          <t xml:space="preserve">Egholmvej 6</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197460</t>
+          <t xml:space="preserve">4197674</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1070,11 +1070,11 @@
         </is>
       </c>
       <c r="H18">
-        <v>253</v>
+        <v>276</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203234</t>
+          <t xml:space="preserve">311203232</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egholmvej 2</t>
+          <t xml:space="preserve">Egholmvej 6</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1121,20 +1121,20 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197672</t>
+          <t xml:space="preserve">4197674</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H19">
-        <v>512</v>
+        <v>282</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203242</t>
+          <t xml:space="preserve">311203232</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1186,11 +1186,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H20">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1246,11 +1246,11 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H21">
-        <v>282</v>
+        <v>499</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1291,30 +1291,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egholmvej 6</t>
+          <t xml:space="preserve">Solhøjvej 12</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">8300</t>
+          <t xml:space="preserve">8350</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197674</t>
+          <t xml:space="preserve">4195321</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H22">
-        <v>294</v>
+        <v>371</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203232</t>
+          <t xml:space="preserve">311203243</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egholmvej 6</t>
+          <t xml:space="preserve">Bronzealdervej 16</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1366,20 +1366,20 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H23">
-        <v>499</v>
+        <v>270</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203232</t>
+          <t xml:space="preserve">311208182</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-28</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 16</t>
+          <t xml:space="preserve">Saloparken 2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1421,20 +1421,20 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197674</t>
+          <t xml:space="preserve">7255382</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H24">
-        <v>270</v>
+        <v>555</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208182</t>
+          <t xml:space="preserve">311208186</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saloparken 2</t>
+          <t xml:space="preserve">Torvald Køhlsvej 50</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">7255382</t>
+          <t xml:space="preserve">9665232</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1490,11 +1490,11 @@
         </is>
       </c>
       <c r="H25">
-        <v>555</v>
+        <v>398</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208186</t>
+          <t xml:space="preserve">311208185</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvald Køhlsvej 50</t>
+          <t xml:space="preserve">Gylling Skolegade 12</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">9665232</t>
+          <t xml:space="preserve">4193329</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1550,16 +1550,16 @@
         </is>
       </c>
       <c r="H26">
-        <v>398</v>
+        <v>442</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208185</t>
+          <t xml:space="preserve">311211745</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-24</t>
+          <t xml:space="preserve">2026-11-11</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gylling Skolegade 12</t>
+          <t xml:space="preserve">Havrevænget 15</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">4193329</t>
+          <t xml:space="preserve">8037533</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1610,11 +1610,11 @@
         </is>
       </c>
       <c r="H27">
-        <v>442</v>
+        <v>327</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311211745</t>
+          <t xml:space="preserve">311211743</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havrevænget 15</t>
+          <t xml:space="preserve">Skolegade 15A</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">8037533</t>
+          <t xml:space="preserve">4193708</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1670,16 +1670,16 @@
         </is>
       </c>
       <c r="H28">
-        <v>327</v>
+        <v>398</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311211743</t>
+          <t xml:space="preserve">311218214</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-11</t>
+          <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 15A</t>
+          <t xml:space="preserve">Venneslaparken 1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">4193708</t>
+          <t xml:space="preserve">7956622</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1730,16 +1730,16 @@
         </is>
       </c>
       <c r="H29">
-        <v>398</v>
+        <v>480</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311218214</t>
+          <t xml:space="preserve">311218471</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-16</t>
+          <t xml:space="preserve">2026-12-19</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -1771,17 +1771,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Venneslaparken 1</t>
+          <t xml:space="preserve">Landevejen 30</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">8300</t>
+          <t xml:space="preserve">8350</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">7956622</t>
+          <t xml:space="preserve">4194779</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1790,16 +1790,16 @@
         </is>
       </c>
       <c r="H30">
-        <v>480</v>
+        <v>275</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311218471</t>
+          <t xml:space="preserve">311221278</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-19</t>
+          <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 1</t>
+          <t xml:space="preserve">Rudevej 100</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">4193843</t>
+          <t xml:space="preserve">9995805</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1850,11 +1850,11 @@
         </is>
       </c>
       <c r="H31">
-        <v>3079</v>
+        <v>894</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221268</t>
+          <t xml:space="preserve">311221240</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 1</t>
+          <t xml:space="preserve">Rudevej 100</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1901,20 +1901,20 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">4193843</t>
+          <t xml:space="preserve">9995805</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H32">
-        <v>695</v>
+        <v>329</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221268</t>
+          <t xml:space="preserve">311221245</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1951,30 +1951,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landevejen 30</t>
+          <t xml:space="preserve">Rudevej 100</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">8350</t>
+          <t xml:space="preserve">8300</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">4194779</t>
+          <t xml:space="preserve">9995805</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H33">
-        <v>275</v>
+        <v>428</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221278</t>
+          <t xml:space="preserve">311221240</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2026,11 +2026,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H34">
-        <v>894</v>
+        <v>1621</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rudevej 100</t>
+          <t xml:space="preserve">Skolevænget 1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2081,20 +2081,20 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">9995805</t>
+          <t xml:space="preserve">4193843</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H35">
-        <v>329</v>
+        <v>3079</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221242</t>
+          <t xml:space="preserve">311221268</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rudevej 100</t>
+          <t xml:space="preserve">Skolevænget 1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">9995805</t>
+          <t xml:space="preserve">4193843</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2150,11 +2150,11 @@
         </is>
       </c>
       <c r="H36">
-        <v>428</v>
+        <v>695</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221240</t>
+          <t xml:space="preserve">311221268</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rudevej 100</t>
+          <t xml:space="preserve">Østermarksvej 25A</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2201,25 +2201,25 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">9995805</t>
+          <t xml:space="preserve">100049247</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H37">
-        <v>1621</v>
+        <v>620</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221240</t>
+          <t xml:space="preserve">311224995</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-06</t>
+          <t xml:space="preserve">2027-01-27</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østermarksvej 25A</t>
+          <t xml:space="preserve">Gylling Skolegade 13</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">100049247</t>
+          <t xml:space="preserve">4193434</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2270,16 +2270,16 @@
         </is>
       </c>
       <c r="H38">
-        <v>620</v>
+        <v>2202</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224995</t>
+          <t xml:space="preserve">311230442</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-27</t>
+          <t xml:space="preserve">2027-02-24</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gylling Skolegade 13</t>
+          <t xml:space="preserve">Nølevvej 4</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">4193434</t>
+          <t xml:space="preserve">7349419</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2330,11 +2330,11 @@
         </is>
       </c>
       <c r="H39">
-        <v>2202</v>
+        <v>11918</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230442</t>
+          <t xml:space="preserve">311230441</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nølevvej 4</t>
+          <t xml:space="preserve">Vennelundsvej 95</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">7349419</t>
+          <t xml:space="preserve">8375804</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2390,16 +2390,16 @@
         </is>
       </c>
       <c r="H40">
-        <v>11918</v>
+        <v>994</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230441</t>
+          <t xml:space="preserve">311242492</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-24</t>
+          <t xml:space="preserve">2027-04-24</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2446,11 +2446,11 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H41">
-        <v>994</v>
+        <v>1212</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2506,11 +2506,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H42">
-        <v>1212</v>
+        <v>1546</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vennelundsvej 95</t>
+          <t xml:space="preserve">Mejerivej 14</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2561,25 +2561,25 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">8375804</t>
+          <t xml:space="preserve">4196620</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H43">
-        <v>1546</v>
+        <v>887</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311242492</t>
+          <t xml:space="preserve">311253199</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-24</t>
+          <t xml:space="preserve">2027-06-12</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mejerivej 14</t>
+          <t xml:space="preserve">Bronzealdervej 10</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2621,25 +2621,25 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196620</t>
+          <t xml:space="preserve">100052507</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H44">
-        <v>887</v>
+        <v>787</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253199</t>
+          <t xml:space="preserve">311258871</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-12</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 2</t>
+          <t xml:space="preserve">Bronzealdervej 12</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H45">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 4</t>
+          <t xml:space="preserve">Bronzealdervej 14</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H46">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 6</t>
+          <t xml:space="preserve">Bronzealdervej 2</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H47">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 8</t>
+          <t xml:space="preserve">Bronzealdervej 4</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2866,15 +2866,15 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H48">
-        <v>324</v>
+        <v>787</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258869</t>
+          <t xml:space="preserve">311258871</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 10</t>
+          <t xml:space="preserve">Bronzealdervej 6</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H49">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 12</t>
+          <t xml:space="preserve">Bronzealdervej 8</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2986,15 +2986,15 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H50">
-        <v>787</v>
+        <v>324</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258871</t>
+          <t xml:space="preserve">311258869</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bronzealdervej 14</t>
+          <t xml:space="preserve">Rådhusgade 38</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3041,25 +3041,25 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052507</t>
+          <t xml:space="preserve">4196668</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H51">
-        <v>787</v>
+        <v>1377</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258871</t>
+          <t xml:space="preserve">311259724</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusgade 38</t>
+          <t xml:space="preserve">Rådhusgade 43</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196668</t>
+          <t xml:space="preserve">4196792</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3110,11 +3110,11 @@
         </is>
       </c>
       <c r="H52">
-        <v>1377</v>
+        <v>1063</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259724</t>
+          <t xml:space="preserve">311259573</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H53">
-        <v>1063</v>
+        <v>1468</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusgade 43</t>
+          <t xml:space="preserve">Aaholmsgade 3A</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3221,25 +3221,25 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196792</t>
+          <t xml:space="preserve">4196607</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H54">
-        <v>1468</v>
+        <v>301</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259573</t>
+          <t xml:space="preserve">311270275</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-09-01</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ålykkecentret 5</t>
+          <t xml:space="preserve">Aaholmsgade 3E</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3286,15 +3286,15 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H55">
-        <v>3261</v>
+        <v>310</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311270273</t>
+          <t xml:space="preserve">311270275</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aaholmsgade 3A</t>
+          <t xml:space="preserve">Ålykkecentret 5</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3346,15 +3346,15 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H56">
-        <v>301</v>
+        <v>3261</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311270275</t>
+          <t xml:space="preserve">311270273</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aaholmsgade 3E</t>
+          <t xml:space="preserve">Stenslund 2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3401,25 +3401,25 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">4196607</t>
+          <t xml:space="preserve">369803</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H57">
-        <v>310</v>
+        <v>545</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311270275</t>
+          <t xml:space="preserve">311271441</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-01</t>
+          <t xml:space="preserve">2027-09-07</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusgade 3</t>
+          <t xml:space="preserve">Banegårdsgade 5</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197028</t>
+          <t xml:space="preserve">8297681</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3530,11 +3530,11 @@
         </is>
       </c>
       <c r="H59">
-        <v>6516</v>
+        <v>700</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311275868</t>
+          <t xml:space="preserve">311275892</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banegårdsgade 5</t>
+          <t xml:space="preserve">Rådhusgade 3</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">8297681</t>
+          <t xml:space="preserve">4197028</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3650,11 +3650,11 @@
         </is>
       </c>
       <c r="H61">
-        <v>700</v>
+        <v>6516</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311275892</t>
+          <t xml:space="preserve">311275868</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311447313</t>
+          <t xml:space="preserve">311447305</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitaparkvej 9</t>
+          <t xml:space="preserve">Præstevænget 28</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3826,15 +3826,15 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H64">
-        <v>1592</v>
+        <v>1313</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555235</t>
+          <t xml:space="preserve">311555233</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitaparkvej 9</t>
+          <t xml:space="preserve">Vitaparkvej 17</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3886,11 +3886,11 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="H65">
-        <v>3377</v>
+        <v>394</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitavej 63</t>
+          <t xml:space="preserve">Vitaparkvej 19</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3946,15 +3946,15 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H66">
-        <v>500</v>
+        <v>1496</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555232</t>
+          <t xml:space="preserve">311555236</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitaparkvej 19</t>
+          <t xml:space="preserve">Vitaparkvej 6</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4006,15 +4006,15 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H67">
-        <v>1496</v>
+        <v>801</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555236</t>
+          <t xml:space="preserve">311555234</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitavej 71</t>
+          <t xml:space="preserve">Vitaparkvej 9</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4066,15 +4066,15 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H68">
-        <v>2608</v>
+        <v>1592</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555232</t>
+          <t xml:space="preserve">311555235</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitaparkvej 17</t>
+          <t xml:space="preserve">Vitaparkvej 9</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4126,11 +4126,11 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H69">
-        <v>394</v>
+        <v>3377</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstevænget 28</t>
+          <t xml:space="preserve">Vitavej 63</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4186,15 +4186,15 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H70">
-        <v>1313</v>
+        <v>500</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555233</t>
+          <t xml:space="preserve">311555232</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitaparkvej 6</t>
+          <t xml:space="preserve">Vitavej 71</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4246,15 +4246,15 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="H71">
-        <v>801</v>
+        <v>2608</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555234</t>
+          <t xml:space="preserve">311555232</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundevej 35A</t>
+          <t xml:space="preserve">Højmarkvej 10</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">10081243</t>
+          <t xml:space="preserve">4197393</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4490,11 +4490,11 @@
         </is>
       </c>
       <c r="H75">
-        <v>850</v>
+        <v>898</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915753</t>
+          <t xml:space="preserve">311915775</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarkvej 10</t>
+          <t xml:space="preserve">Lundevej 35A</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">4197393</t>
+          <t xml:space="preserve">10081243</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4550,11 +4550,11 @@
         </is>
       </c>
       <c r="H76">
-        <v>898</v>
+        <v>850</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915775</t>
+          <t xml:space="preserve">311915753</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østermarksvej 21</t>
+          <t xml:space="preserve">Parkvej 5</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4601,20 +4601,20 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">4198344</t>
+          <t xml:space="preserve">500006, 4198718</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H77">
-        <v>569</v>
+        <v>1568</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915750</t>
+          <t xml:space="preserve">311915754</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østermarksvej 21B</t>
+          <t xml:space="preserve">Parkvej 5</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4661,20 +4661,20 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">4198348</t>
+          <t xml:space="preserve">500006, 4198718</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H78">
-        <v>555</v>
+        <v>1560</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915749</t>
+          <t xml:space="preserve">311915754</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4721,16 +4721,16 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">500006, 4198718</t>
+          <t xml:space="preserve">500006, 500007, 4198718</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H79">
-        <v>1568</v>
+        <v>3017</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4781,20 +4781,20 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">500006, 4198718</t>
+          <t xml:space="preserve">500007, 4198718</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H80">
-        <v>1560</v>
+        <v>332</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915754</t>
+          <t xml:space="preserve">311915756</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 5</t>
+          <t xml:space="preserve">Østermarksvej 21</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4841,20 +4841,20 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">500006, 500007, 4198718</t>
+          <t xml:space="preserve">4198344</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H81">
-        <v>3017</v>
+        <v>569</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915754</t>
+          <t xml:space="preserve">311915750</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parkvej 5</t>
+          <t xml:space="preserve">Østermarksvej 21B</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4901,20 +4901,20 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">500007, 4198718</t>
+          <t xml:space="preserve">4198348</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H82">
-        <v>332</v>
+        <v>555</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915756</t>
+          <t xml:space="preserve">311915749</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">

--- a/public/exports/32264328.xlsx
+++ b/public/exports/32264328.xlsx
@@ -1854,7 +1854,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221240</t>
+          <t xml:space="preserve">311221245</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221240</t>
+          <t xml:space="preserve">311221245</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221240</t>
+          <t xml:space="preserve">311221245</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">

--- a/public/exports/32264328.xlsx
+++ b/public/exports/32264328.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L82"/>
+  <dimension ref="A1:M82"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -899,15 +969,20 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Ålborg)</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-01-19</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -959,15 +1034,20 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-28</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1019,15 +1099,20 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-28</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1079,15 +1164,20 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-28</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1139,15 +1229,20 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-28</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1199,15 +1294,20 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-28</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1259,15 +1359,20 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-28</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1319,15 +1424,20 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-28</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1379,15 +1489,20 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1439,15 +1554,20 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1499,15 +1619,20 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1559,15 +1684,20 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-11</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1619,15 +1749,20 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-11</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1679,15 +1814,20 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1739,15 +1879,20 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-19</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1799,15 +1944,20 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1859,15 +2009,20 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1919,15 +2074,20 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1979,15 +2139,20 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2039,15 +2204,20 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2099,15 +2269,20 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2159,15 +2334,20 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2219,15 +2399,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bornak Arkitekter</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-27</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2279,15 +2464,20 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-24</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2339,15 +2529,20 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-24</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2399,15 +2594,20 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-24</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2459,15 +2659,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-24</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2519,15 +2724,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-24</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-12</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2699,15 +2919,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2759,15 +2984,20 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2819,15 +3049,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2879,15 +3114,20 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2939,15 +3179,20 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2999,15 +3244,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3179,15 +3439,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-01</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3299,15 +3569,20 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-01</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3359,15 +3634,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-01</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-07</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-28</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-29</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-29</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-09-29</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3719,15 +4024,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-07</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3774,20 +4084,25 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311447305</t>
+          <t xml:space="preserve">311447313</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve">John Klysner Consult ApS</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-07-01</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-14</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4319,15 +4674,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Boligtjek ApS</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-18</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Boligtjek ApS</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-02</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tæthedskompagniet ApS</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-08</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4679,15 +5064,20 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4919,21 +5324,26 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L82"/>
+  <autoFilter ref="A1:M82"/>
 </worksheet>
 </file>
--- a/public/exports/32264328.xlsx
+++ b/public/exports/32264328.xlsx
@@ -2004,7 +2004,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221245</t>
+          <t xml:space="preserve">311221240</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221245</t>
+          <t xml:space="preserve">311221242</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221245</t>
+          <t xml:space="preserve">311221240</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221245</t>
+          <t xml:space="preserve">311221240</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311447313</t>
+          <t xml:space="preserve">311447305</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
